--- a/data/EVALUACIONES/FUERZA TREN SUPERIOR/FUERZA_TS.xlsx
+++ b/data/EVALUACIONES/FUERZA TREN SUPERIOR/FUERZA_TS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30405"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\FUERZA TREN SUPERIOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760DCE63-E3D2-4ED1-B983-AC2AC023C3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1883E00-720B-4177-87FA-7852F81ED79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Fecha</t>
   </si>
@@ -99,9 +99,6 @@
     <t>Petko_Avramov</t>
   </si>
   <si>
-    <t xml:space="preserve">Luca _Valentino_Scaffetti </t>
-  </si>
-  <si>
     <t>Jorge_vicaria</t>
   </si>
   <si>
@@ -115,13 +112,22 @@
   </si>
   <si>
     <t>Jaime_Munoz_Garcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan_Manuel_Ruiz </t>
+  </si>
+  <si>
+    <t>Alex_Palacios</t>
+  </si>
+  <si>
+    <t>Presley_Osarenkhoe</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,11 +140,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF434343"/>
-      <name val="Roboto"/>
     </font>
   </fonts>
   <fills count="3">
@@ -167,12 +168,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -219,8 +219,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47DCDBC4-934F-4BB8-8403-1163E6A946CF}" name="Tabla1" displayName="Tabla1" ref="A1:D53" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="A1:D53" xr:uid="{F24D9BFF-4F02-4AC6-9C99-CC9D7330899E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47DCDBC4-934F-4BB8-8403-1163E6A946CF}" name="Tabla1" displayName="Tabla1" ref="A1:D29" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="A1:D29" xr:uid="{F24D9BFF-4F02-4AC6-9C99-CC9D7330899E}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{B90CC2EA-DED7-4B50-9C01-6648707B7686}" name="Fecha" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{49BFBD1B-88C4-49EF-ACC0-907CF6D29923}" name="Nombre"/>
@@ -528,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF0B100-72AE-4E6A-8897-D79B621AF892}">
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
@@ -544,200 +544,194 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D6" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D7" s="1">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C9" s="1">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D9" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C11" s="1">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D11" s="1">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D12" s="1">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="1">
-        <v>22</v>
-      </c>
-      <c r="D13" s="1">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C14" s="1">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D14" s="1">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C15" s="1">
         <v>24</v>
@@ -748,181 +742,181 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C16" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D16" s="1">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D17" s="1">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C18" s="1">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D18" s="1">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C19" s="1">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D19" s="1">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C20" s="1">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D20" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C21" s="1">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D21" s="1">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C22" s="1">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D22" s="1">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C23" s="1">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D23" s="1">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>46569</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>24</v>
+        <v>46247</v>
+      </c>
+      <c r="B24" t="s">
+        <v>4</v>
       </c>
       <c r="C24" s="1">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D24" s="1">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C25" s="1">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="D25" s="1">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C26" s="1">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="D26" s="1">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>46569</v>
+        <v>46247</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C27" s="1">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D27" s="1">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>46600</v>
+        <v>46247</v>
       </c>
       <c r="B28" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C28" s="1">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="D28" s="1">
         <v>23</v>
@@ -930,352 +924,16 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>46600</v>
+        <v>46247</v>
       </c>
       <c r="B29" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C29" s="1">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="D29" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B30" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" s="1">
-        <v>30</v>
-      </c>
-      <c r="D30" s="1">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B31" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="1">
-        <v>29</v>
-      </c>
-      <c r="D31" s="1">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B32" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="1">
-        <v>28</v>
-      </c>
-      <c r="D32" s="1">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="1">
-        <v>27</v>
-      </c>
-      <c r="D33" s="1">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="1">
-        <v>26</v>
-      </c>
-      <c r="D34" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="1">
-        <v>25</v>
-      </c>
-      <c r="D35" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B36" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="1">
-        <v>24</v>
-      </c>
-      <c r="D36" s="1">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B37" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="1">
-        <v>23</v>
-      </c>
-      <c r="D37" s="1">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B38" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38" s="1">
-        <v>22</v>
-      </c>
-      <c r="D38" s="1">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B39" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" s="1">
         <v>21</v>
-      </c>
-      <c r="D39" s="1">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B40" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" s="1">
-        <v>20</v>
-      </c>
-      <c r="D40" s="1">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B41" t="s">
-        <v>15</v>
-      </c>
-      <c r="C41" s="1">
-        <v>19</v>
-      </c>
-      <c r="D41" s="1">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" s="1">
-        <v>18</v>
-      </c>
-      <c r="D42" s="1">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B43" t="s">
-        <v>17</v>
-      </c>
-      <c r="C43" s="1">
-        <v>17</v>
-      </c>
-      <c r="D43" s="1">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B44" t="s">
-        <v>18</v>
-      </c>
-      <c r="C44" s="1">
-        <v>16</v>
-      </c>
-      <c r="D44" s="1">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B45" t="s">
-        <v>19</v>
-      </c>
-      <c r="C45" s="1">
-        <v>15</v>
-      </c>
-      <c r="D45" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B46" t="s">
-        <v>20</v>
-      </c>
-      <c r="C46" s="1">
-        <v>14</v>
-      </c>
-      <c r="D46" s="1">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B47" t="s">
-        <v>21</v>
-      </c>
-      <c r="C47" s="1">
-        <v>13</v>
-      </c>
-      <c r="D47" s="1">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C48" s="1">
-        <v>12</v>
-      </c>
-      <c r="D48" s="1">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B49" t="s">
-        <v>23</v>
-      </c>
-      <c r="C49" s="1">
-        <v>11</v>
-      </c>
-      <c r="D49" s="1">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="1">
-        <v>10</v>
-      </c>
-      <c r="D50" s="1">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B51" t="s">
-        <v>29</v>
-      </c>
-      <c r="C51" s="1">
-        <v>9</v>
-      </c>
-      <c r="D51" s="1">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B52" t="s">
-        <v>25</v>
-      </c>
-      <c r="C52" s="1">
-        <v>8</v>
-      </c>
-      <c r="D52" s="1">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B53" t="s">
-        <v>26</v>
-      </c>
-      <c r="C53" s="1">
-        <v>7</v>
-      </c>
-      <c r="D53" s="1">
-        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/data/EVALUACIONES/FUERZA TREN SUPERIOR/FUERZA_TS.xlsx
+++ b/data/EVALUACIONES/FUERZA TREN SUPERIOR/FUERZA_TS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30405"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30411"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\FUERZA TREN SUPERIOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1883E00-720B-4177-87FA-7852F81ED79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F8F036-2E0B-4CFC-8633-B9ADFED223AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
@@ -127,7 +127,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,13 +136,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -155,8 +164,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -164,48 +185,64 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -216,19 +253,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{47DCDBC4-934F-4BB8-8403-1163E6A946CF}" name="Tabla1" displayName="Tabla1" ref="A1:D29" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="A1:D29" xr:uid="{F24D9BFF-4F02-4AC6-9C99-CC9D7330899E}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{B90CC2EA-DED7-4B50-9C01-6648707B7686}" name="Fecha" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{49BFBD1B-88C4-49EF-ACC0-907CF6D29923}" name="Nombre"/>
-    <tableColumn id="9" xr3:uid="{DBC82145-17DD-41DC-B74C-F4F573017255}" name="PRESS_BANCA_40KG_40S" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{722C034B-F78D-4936-9D99-936E2D8A16F1}" name="DOMINADA_30S" dataDxfId="0"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -532,415 +556,414 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="10" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="5">
+        <v>46247</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="6">
         <v>14</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="7">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="6">
         <v>8</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="7">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="5">
+        <v>46247</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="6">
         <v>12</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="7">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="6">
         <v>7</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="7">
         <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="A6" s="5">
+        <v>46247</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="6">
         <v>12</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="7">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="A7" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="6">
         <v>5</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="7">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="A8" s="5">
+        <v>46247</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="6">
         <v>12</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="7">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="A9" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="6">
         <v>6</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="7">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="A10" s="5">
+        <v>46247</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="6">
         <v>12</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="7">
         <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="A11" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="6">
         <v>8</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="7">
         <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="A12" s="5">
+        <v>46247</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="6">
         <v>9</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="7">
         <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="A13" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="A14" s="5">
+        <v>46247</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="6">
         <v>11</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="7">
         <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="A15" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="6">
         <v>24</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="7">
         <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="A16" s="5">
+        <v>46247</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="6">
         <v>1</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="7">
         <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="A17" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="6">
         <v>12</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="7">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="A18" s="5">
+        <v>46247</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="6">
         <v>4</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="7">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="A19" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="6">
         <v>8</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="7">
         <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="A20" s="5">
+        <v>46247</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="6">
         <v>11</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="7">
         <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="A21" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="6">
         <v>6</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="7">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="A22" s="5">
+        <v>46247</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="6">
         <v>7</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="7">
         <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="A23" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="6">
         <v>10</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="7">
         <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="A24" s="5">
+        <v>46247</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="6">
         <v>10</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="7">
         <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="A25" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="6">
         <v>3</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" s="7">
         <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="A26" s="5">
+        <v>46247</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="6">
         <v>7</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" s="7">
         <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="A27" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="6">
         <v>10</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" s="7">
         <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="A28" s="5">
+        <v>46247</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="6">
         <v>5</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" s="7">
         <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
-        <v>46247</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="A29" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="6">
         <v>4</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29" s="7">
         <v>21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/data/EVALUACIONES/FUERZA TREN SUPERIOR/FUERZA_TS.xlsx
+++ b/data/EVALUACIONES/FUERZA TREN SUPERIOR/FUERZA_TS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\FUERZA TREN SUPERIOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F8F036-2E0B-4CFC-8633-B9ADFED223AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6261C80-B896-4FC3-BC9E-E3378AB8CEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
@@ -581,11 +581,11 @@
       <c r="B2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="7">
+        <v>21</v>
+      </c>
+      <c r="D2" s="6">
         <v>14</v>
-      </c>
-      <c r="D2" s="7">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -595,11 +595,11 @@
       <c r="B3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="7">
+        <v>26</v>
+      </c>
+      <c r="D3" s="6">
         <v>8</v>
-      </c>
-      <c r="D3" s="7">
-        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -609,11 +609,11 @@
       <c r="B4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="7">
+        <v>23</v>
+      </c>
+      <c r="D4" s="6">
         <v>12</v>
-      </c>
-      <c r="D4" s="7">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -623,11 +623,11 @@
       <c r="B5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="7">
+        <v>27</v>
+      </c>
+      <c r="D5" s="6">
         <v>7</v>
-      </c>
-      <c r="D5" s="7">
-        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -637,11 +637,11 @@
       <c r="B6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="7">
+        <v>14</v>
+      </c>
+      <c r="D6" s="6">
         <v>12</v>
-      </c>
-      <c r="D6" s="7">
-        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -651,11 +651,11 @@
       <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="7">
+        <v>9</v>
+      </c>
+      <c r="D7" s="6">
         <v>5</v>
-      </c>
-      <c r="D7" s="7">
-        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -665,11 +665,11 @@
       <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="7">
+        <v>21</v>
+      </c>
+      <c r="D8" s="6">
         <v>12</v>
-      </c>
-      <c r="D8" s="7">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -679,11 +679,11 @@
       <c r="B9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="7">
+        <v>20</v>
+      </c>
+      <c r="D9" s="6">
         <v>6</v>
-      </c>
-      <c r="D9" s="7">
-        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -693,11 +693,11 @@
       <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="7">
+        <v>27</v>
+      </c>
+      <c r="D10" s="6">
         <v>12</v>
-      </c>
-      <c r="D10" s="7">
-        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -707,11 +707,11 @@
       <c r="B11" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="7">
+        <v>28</v>
+      </c>
+      <c r="D11" s="6">
         <v>8</v>
-      </c>
-      <c r="D11" s="7">
-        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -721,11 +721,11 @@
       <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="7">
+        <v>27</v>
+      </c>
+      <c r="D12" s="6">
         <v>9</v>
-      </c>
-      <c r="D12" s="7">
-        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -735,8 +735,8 @@
       <c r="B13" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="6"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
@@ -745,11 +745,11 @@
       <c r="B14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="7">
+        <v>35</v>
+      </c>
+      <c r="D14" s="6">
         <v>11</v>
-      </c>
-      <c r="D14" s="7">
-        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -759,10 +759,10 @@
       <c r="B15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="7">
         <v>24</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="6">
         <v>24</v>
       </c>
     </row>
@@ -773,11 +773,11 @@
       <c r="B16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="7">
+        <v>21</v>
+      </c>
+      <c r="D16" s="6">
         <v>1</v>
-      </c>
-      <c r="D16" s="7">
-        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -787,11 +787,11 @@
       <c r="B17" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="7">
+        <v>20</v>
+      </c>
+      <c r="D17" s="6">
         <v>12</v>
-      </c>
-      <c r="D17" s="7">
-        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -801,11 +801,11 @@
       <c r="B18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="7">
+        <v>22</v>
+      </c>
+      <c r="D18" s="6">
         <v>4</v>
-      </c>
-      <c r="D18" s="7">
-        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -815,11 +815,11 @@
       <c r="B19" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="7">
+        <v>21</v>
+      </c>
+      <c r="D19" s="6">
         <v>8</v>
-      </c>
-      <c r="D19" s="7">
-        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -829,11 +829,11 @@
       <c r="B20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="7">
+        <v>27</v>
+      </c>
+      <c r="D20" s="6">
         <v>11</v>
-      </c>
-      <c r="D20" s="7">
-        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -843,11 +843,11 @@
       <c r="B21" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="7">
+        <v>22</v>
+      </c>
+      <c r="D21" s="6">
         <v>6</v>
-      </c>
-      <c r="D21" s="7">
-        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -857,11 +857,11 @@
       <c r="B22" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="7">
+        <v>37</v>
+      </c>
+      <c r="D22" s="6">
         <v>7</v>
-      </c>
-      <c r="D22" s="7">
-        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -871,11 +871,11 @@
       <c r="B23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="7">
+        <v>33</v>
+      </c>
+      <c r="D23" s="6">
         <v>10</v>
-      </c>
-      <c r="D23" s="7">
-        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -885,11 +885,11 @@
       <c r="B24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="7">
+        <v>13</v>
+      </c>
+      <c r="D24" s="6">
         <v>10</v>
-      </c>
-      <c r="D24" s="7">
-        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -899,11 +899,11 @@
       <c r="B25" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="7">
+        <v>12</v>
+      </c>
+      <c r="D25" s="6">
         <v>3</v>
-      </c>
-      <c r="D25" s="7">
-        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -913,11 +913,11 @@
       <c r="B26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="7">
+        <v>29</v>
+      </c>
+      <c r="D26" s="6">
         <v>7</v>
-      </c>
-      <c r="D26" s="7">
-        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -927,11 +927,11 @@
       <c r="B27" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="7">
+        <v>30</v>
+      </c>
+      <c r="D27" s="6">
         <v>10</v>
-      </c>
-      <c r="D27" s="7">
-        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -941,11 +941,11 @@
       <c r="B28" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="7">
+        <v>23</v>
+      </c>
+      <c r="D28" s="6">
         <v>5</v>
-      </c>
-      <c r="D28" s="7">
-        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -955,11 +955,11 @@
       <c r="B29" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="7">
+        <v>21</v>
+      </c>
+      <c r="D29" s="6">
         <v>4</v>
-      </c>
-      <c r="D29" s="7">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/data/EVALUACIONES/FUERZA TREN SUPERIOR/FUERZA_TS.xlsx
+++ b/data/EVALUACIONES/FUERZA TREN SUPERIOR/FUERZA_TS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\FUERZA TREN SUPERIOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6261C80-B896-4FC3-BC9E-E3378AB8CEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755691EC-33C3-4437-A31E-D0E3F073D7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
@@ -177,7 +177,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -222,27 +222,115 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -253,6 +341,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4038579-32CC-4315-96AE-2AFD5D4E1DEC}" name="Tabla1" displayName="Tabla1" ref="A1:D29" totalsRowShown="0" headerRowBorderDxfId="2" tableBorderDxfId="3">
+  <autoFilter ref="A1:D29" xr:uid="{A4038579-32CC-4315-96AE-2AFD5D4E1DEC}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{07CF568F-C355-412E-AF62-0FC68FE004D5}" name="Fecha"/>
+    <tableColumn id="2" xr3:uid="{61A0F3E6-BA24-4229-B91D-142FB098244E}" name="Nombre"/>
+    <tableColumn id="3" xr3:uid="{A70B4B5D-707A-4239-9A21-451210448FB8}" name="PRESS_BANCA_40KG_40S" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{43B876AD-D271-41DD-8788-200B665BEAD6}" name="DOMINADA_30S" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -556,15 +657,15 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.44140625" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
@@ -575,395 +676,398 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="5">
-        <v>46247</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="5">
         <v>21</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="4">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
-        <v>46247</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="A3" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="5">
         <v>26</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="4">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
-        <v>46247</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <v>23</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
-        <v>46247</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="5">
         <v>27</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
-        <v>46247</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>14</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
-        <v>46247</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="A7" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <v>9</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
-        <v>46247</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <v>21</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
-        <v>46247</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="A9" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="5">
         <v>20</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
-        <v>46247</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="5">
         <v>27</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
-        <v>46247</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="A11" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="5">
         <v>28</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="4">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="5">
-        <v>46247</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="A12" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="5">
         <v>27</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="4">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
-        <v>46247</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="A13" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="6"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="4"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="5">
-        <v>46247</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="A14" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="5">
         <v>35</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="4">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
-        <v>46247</v>
-      </c>
-      <c r="B15" s="4" t="s">
+      <c r="A15" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="7">
-        <v>24</v>
-      </c>
-      <c r="D15" s="6">
-        <v>24</v>
+      <c r="C15" s="5">
+        <v>21</v>
+      </c>
+      <c r="D15" s="4">
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="5">
-        <v>46247</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="A16" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="5">
         <v>21</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
-        <v>46247</v>
-      </c>
-      <c r="B17" s="4" t="s">
+      <c r="A17" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="5">
         <v>20</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="4">
         <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="5">
-        <v>46247</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="A18" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="5">
         <v>22</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="4">
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
-        <v>46247</v>
-      </c>
-      <c r="B19" s="4" t="s">
+      <c r="A19" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="5">
         <v>21</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="4">
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="5">
-        <v>46247</v>
-      </c>
-      <c r="B20" s="3" t="s">
+      <c r="A20" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="5">
         <v>27</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="4">
         <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
-        <v>46247</v>
-      </c>
-      <c r="B21" s="4" t="s">
+      <c r="A21" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="5">
         <v>22</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="5">
-        <v>46247</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="A22" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="5">
         <v>37</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="4">
         <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="8">
-        <v>46247</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="A23" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="5">
         <v>33</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="5">
-        <v>46247</v>
-      </c>
-      <c r="B24" s="3" t="s">
+      <c r="A24" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="5">
         <v>13</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="8">
-        <v>46247</v>
-      </c>
-      <c r="B25" s="4" t="s">
+      <c r="A25" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="5">
         <v>12</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="5">
-        <v>46247</v>
-      </c>
-      <c r="B26" s="3" t="s">
+      <c r="A26" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="5">
         <v>29</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="4">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="8">
-        <v>46247</v>
-      </c>
-      <c r="B27" s="4" t="s">
+      <c r="A27" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="5">
         <v>30</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="5">
-        <v>46247</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="A28" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="5">
         <v>23</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="8">
-        <v>46247</v>
-      </c>
-      <c r="B29" s="4" t="s">
+      <c r="A29" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="5">
         <v>21</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="4">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>